--- a/Excel Formulas .xlsx
+++ b/Excel Formulas .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shaik\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C01C90F-EA7F-4B27-B691-63C1BEEA5EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7535FDD5-492F-48A1-BEFA-95DC517B3651}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12720" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IF FORMULA" sheetId="15" r:id="rId1"/>
@@ -45,17 +45,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1180,6 +1169,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1195,21 +1199,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1219,26 +1208,6 @@
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1356,6 +1325,26 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1704,12 +1693,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="sk" displayName="sk" ref="A1:C16" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="sk" displayName="sk" ref="A1:C16" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Employee Code" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Designation" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Salary" dataDxfId="2" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Employee Code" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Designation" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Salary" dataDxfId="0" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1979,15 +1968,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -2007,7 +1996,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43739</v>
       </c>
@@ -2025,7 +2014,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43740</v>
       </c>
@@ -2040,7 +2029,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43741</v>
       </c>
@@ -2052,7 +2041,7 @@
       </c>
       <c r="D4" s="51"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -2070,7 +2059,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43743</v>
       </c>
@@ -2085,7 +2074,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43744</v>
       </c>
@@ -2097,7 +2086,7 @@
       </c>
       <c r="D7" s="51"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43745</v>
       </c>
@@ -2115,7 +2104,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43746</v>
       </c>
@@ -2130,7 +2119,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43747</v>
       </c>
@@ -2142,7 +2131,7 @@
       </c>
       <c r="D10" s="51"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43748</v>
       </c>
@@ -2154,7 +2143,7 @@
       </c>
       <c r="D11" s="51"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43749</v>
       </c>
@@ -2166,7 +2155,7 @@
       </c>
       <c r="D12" s="51"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43750</v>
       </c>
@@ -2187,15 +2176,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -2209,7 +2198,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="41">
         <v>43740</v>
       </c>
@@ -2223,7 +2212,7 @@
         <v>20588</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <v>43742</v>
       </c>
@@ -2237,7 +2226,7 @@
         <v>42392</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>43745</v>
       </c>
@@ -2251,7 +2240,7 @@
         <v>16334</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>43746</v>
       </c>
@@ -2265,7 +2254,7 @@
         <v>24400</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>43744</v>
       </c>
@@ -2279,7 +2268,7 @@
         <v>44441</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>43747</v>
       </c>
@@ -2293,7 +2282,7 @@
         <v>32074</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>44062</v>
       </c>
@@ -2307,7 +2296,7 @@
         <v>33268</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>43750</v>
       </c>
@@ -2321,7 +2310,7 @@
         <v>19887</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="41">
         <v>43739</v>
       </c>
@@ -2335,7 +2324,7 @@
         <v>41659</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="41">
         <v>43741</v>
       </c>
@@ -2349,7 +2338,7 @@
         <v>17770</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <v>43743</v>
       </c>
@@ -2363,7 +2352,7 @@
         <v>16888</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="41">
         <v>43749</v>
       </c>
@@ -2386,14 +2375,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -2410,7 +2399,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43739</v>
       </c>
@@ -2427,7 +2416,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43740</v>
       </c>
@@ -2441,7 +2430,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43741</v>
       </c>
@@ -2455,7 +2444,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -2475,7 +2464,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43743</v>
       </c>
@@ -2495,7 +2484,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43744</v>
       </c>
@@ -2512,7 +2501,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43745</v>
       </c>
@@ -2526,7 +2515,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43746</v>
       </c>
@@ -2540,7 +2529,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43747</v>
       </c>
@@ -2554,7 +2543,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43748</v>
       </c>
@@ -2568,7 +2557,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43749</v>
       </c>
@@ -2591,7 +2580,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43750</v>
       </c>
@@ -2614,7 +2603,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K14" t="s">
         <v>207</v>
       </c>
@@ -2628,19 +2617,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D1" s="3" t="s">
         <v>65</v>
       </c>
@@ -2654,7 +2643,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>152</v>
       </c>
@@ -2662,7 +2651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>153</v>
       </c>
@@ -2670,7 +2659,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -2678,7 +2667,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -2686,7 +2675,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>156</v>
       </c>
@@ -2694,7 +2683,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>157</v>
       </c>
@@ -2702,7 +2691,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -2710,7 +2699,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
@@ -2718,7 +2707,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>160</v>
       </c>
@@ -2726,7 +2715,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>161</v>
       </c>
@@ -2734,7 +2723,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>162</v>
       </c>
@@ -2742,7 +2731,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>163</v>
       </c>
@@ -2750,157 +2739,157 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>194</v>
       </c>
@@ -2914,13 +2903,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>195</v>
       </c>
@@ -2940,7 +2929,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>152</v>
       </c>
@@ -2948,7 +2937,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>153</v>
       </c>
@@ -2956,7 +2945,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -2964,7 +2953,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -2972,7 +2961,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>156</v>
       </c>
@@ -2980,7 +2969,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>157</v>
       </c>
@@ -2988,7 +2977,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -2996,7 +2985,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
@@ -3004,7 +2993,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>160</v>
       </c>
@@ -3012,7 +3001,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>161</v>
       </c>
@@ -3020,7 +3009,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>162</v>
       </c>
@@ -3028,7 +3017,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>163</v>
       </c>
@@ -3036,7 +3025,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>164</v>
       </c>
@@ -3044,7 +3033,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>165</v>
       </c>
@@ -3052,7 +3041,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>166</v>
       </c>
@@ -3060,7 +3049,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>167</v>
       </c>
@@ -3068,7 +3057,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>168</v>
       </c>
@@ -3076,132 +3065,132 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>194</v>
       </c>
@@ -3215,22 +3204,22 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="61"/>
+      <c r="B1" s="56"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>106</v>
       </c>
@@ -3238,25 +3227,25 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>104</v>
       </c>
       <c r="B3" s="20"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>103</v>
       </c>
       <c r="B4" s="20"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>102</v>
       </c>
       <c r="B5" s="20"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>101</v>
       </c>
@@ -3274,30 +3263,30 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
     <col min="8" max="9" width="14" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="53"/>
+      <c r="C1" s="58"/>
       <c r="F1" s="13" t="s">
         <v>87</v>
       </c>
@@ -3310,16 +3299,16 @@
       <c r="I1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="K1" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="55"/>
-      <c r="N1" s="56" t="s">
+      <c r="L1" s="60"/>
+      <c r="N1" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="O1" s="56"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O1" s="61"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>95</v>
       </c>
@@ -3339,7 +3328,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>93</v>
       </c>
@@ -3374,7 +3363,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>82</v>
       </c>
@@ -3406,7 +3395,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
         <v>88</v>
       </c>
@@ -3438,7 +3427,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C6" s="1"/>
       <c r="F6" s="1">
         <v>5</v>
@@ -3447,7 +3436,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>84</v>
       </c>
@@ -3470,7 +3459,7 @@
       </c>
       <c r="O7" s="9"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>80</v>
       </c>
@@ -3486,7 +3475,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
@@ -3502,7 +3491,7 @@
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F10" s="1">
         <v>9</v>
       </c>
@@ -3510,7 +3499,7 @@
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C11" s="6"/>
       <c r="F11" s="1">
         <v>10</v>
@@ -3519,25 +3508,25 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F12" s="1"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H14" s="17"/>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" s="42"/>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" s="43"/>
     </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D24" s="25"/>
     </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D25" s="43"/>
     </row>
   </sheetData>
@@ -3555,57 +3544,57 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD370CA7-072E-401D-B6DB-B596C19532A0}">
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
       <c r="C3" s="41">
         <f ca="1">A3+B3</f>
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="D3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4" s="41">
         <f ca="1">A4-B4</f>
-        <v>46222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="50">
         <f ca="1">NOW()</f>
-        <v>46227.540200578704</v>
+        <v>46245.642577662038</v>
       </c>
       <c r="C6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <f ca="1">YEAR(A6)</f>
         <v>2026</v>
@@ -3614,88 +3603,88 @@
         <v>223</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <f ca="1">MONTH(A6)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <f ca="1">DAY(A6)</f>
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <f ca="1">DATE(A8,A9,A10)</f>
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="C12" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f ca="1">TEXT(A6,"dddd")</f>
-        <v>Friday</v>
+        <v>Tuesday</v>
       </c>
       <c r="B14" t="str">
         <f ca="1">TEXT(A6,"mmmm")</f>
-        <v>July</v>
+        <v>August</v>
       </c>
       <c r="C14" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f ca="1">TEXT(A12,"ddd")</f>
-        <v>Fri</v>
+        <v>Tue</v>
       </c>
       <c r="B15" t="str">
         <f ca="1">TEXT(A6,"mmm")</f>
-        <v>Jul</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>Aug</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f ca="1">TEXT(A12,"dd")</f>
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B16" t="str">
         <f ca="1">TEXT(A6,"mm")</f>
-        <v>07</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f ca="1">TEXT(A6,"m")</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f ca="1">TEXT(A12,"mmm-yy")</f>
-        <v>Jul-26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>Aug-26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <f ca="1">WEEKDAY(A12,11)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="41">
         <v>46113</v>
       </c>
@@ -3707,29 +3696,29 @@
         <v>213</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C22">
         <f>_xlfn.DAYS(B21,A21)</f>
         <v>213</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C23">
         <f>DAYS360(A21,B21,)</f>
         <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>46113</v>
       </c>
@@ -3741,19 +3730,19 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C28">
         <f>_xlfn.DAYS(B27,A27)</f>
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C29">
         <f>DAYS360(A27,B27)</f>
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>46127</v>
       </c>
@@ -3768,7 +3757,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C32" s="41">
         <f>EOMONTH(A31,B31)</f>
         <v>46326</v>
@@ -3777,7 +3766,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>46127</v>
       </c>
@@ -3785,17 +3774,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="41">
         <v>46113</v>
       </c>
@@ -3816,7 +3805,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C40">
         <f>NETWORKDAYS.INTL(A38,B38,11,)</f>
         <v>184</v>
@@ -3836,17 +3825,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -3863,7 +3852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43739</v>
       </c>
@@ -3884,7 +3873,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43740</v>
       </c>
@@ -3905,7 +3894,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43741</v>
       </c>
@@ -3932,7 +3921,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -3952,7 +3941,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43743</v>
       </c>
@@ -3973,7 +3962,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43744</v>
       </c>
@@ -3990,7 +3979,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43745</v>
       </c>
@@ -4011,7 +4000,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43746</v>
       </c>
@@ -4028,7 +4017,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43747</v>
       </c>
@@ -4049,7 +4038,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43748</v>
       </c>
@@ -4064,7 +4053,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43749</v>
       </c>
@@ -4079,7 +4068,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43750</v>
       </c>
@@ -4103,16 +4092,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -4140,7 +4129,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43739</v>
       </c>
@@ -4164,7 +4153,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43740</v>
       </c>
@@ -4182,7 +4171,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43741</v>
       </c>
@@ -4197,7 +4186,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -4215,7 +4204,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43743</v>
       </c>
@@ -4233,7 +4222,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43744</v>
       </c>
@@ -4251,7 +4240,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43745</v>
       </c>
@@ -4266,7 +4255,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43746</v>
       </c>
@@ -4281,7 +4270,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43747</v>
       </c>
@@ -4296,7 +4285,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43748</v>
       </c>
@@ -4311,7 +4300,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43749</v>
       </c>
@@ -4326,7 +4315,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43750</v>
       </c>
@@ -4350,43 +4339,43 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="21" width="2.6640625" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" customWidth="1"/>
+    <col min="3" max="21" width="2.7109375" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>COUNT(C3:T15)</f>
         <v>0</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="59"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="54"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>COUNTA(C3:U15,)</f>
         <v>137</v>
@@ -4452,7 +4441,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
@@ -4496,7 +4485,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>45</v>
       </c>
@@ -4539,7 +4528,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
@@ -4585,7 +4574,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
@@ -4625,7 +4614,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
         <v>45</v>
       </c>
@@ -4672,7 +4661,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
         <v>45</v>
       </c>
@@ -4719,7 +4708,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
@@ -4774,7 +4763,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
@@ -4815,7 +4804,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
@@ -4848,7 +4837,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
@@ -4881,7 +4870,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
@@ -4914,7 +4903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
@@ -4952,10 +4941,10 @@
     <mergeCell ref="C2:U2"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:U15">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"M"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4967,15 +4956,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>13</v>
       </c>
@@ -4989,7 +4978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>20</v>
       </c>
@@ -5003,7 +4992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>25</v>
       </c>
@@ -5017,7 +5006,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>24</v>
       </c>
@@ -5028,7 +5017,7 @@
         <v>26895</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>22</v>
       </c>
@@ -5039,7 +5028,7 @@
         <v>29264</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>27</v>
       </c>
@@ -5050,7 +5039,7 @@
         <v>36505</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>18</v>
       </c>
@@ -5062,7 +5051,7 @@
       </c>
       <c r="G7" s="27"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>16</v>
       </c>
@@ -5073,7 +5062,7 @@
         <v>34141</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>23</v>
       </c>
@@ -5084,7 +5073,7 @@
         <v>32914</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
@@ -5095,7 +5084,7 @@
         <v>37908</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
@@ -5106,7 +5095,7 @@
         <v>28875</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>30</v>
       </c>
@@ -5117,7 +5106,7 @@
         <v>36135</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>28</v>
       </c>
@@ -5128,7 +5117,7 @@
         <v>31711</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
         <v>200</v>
       </c>
@@ -5139,7 +5128,7 @@
         <v>38791</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
         <v>201</v>
       </c>
@@ -5150,7 +5139,7 @@
         <v>38598</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="48" t="s">
         <v>202</v>
       </c>
@@ -5161,71 +5150,71 @@
         <v>27678</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C18" s="29"/>
       <c r="D18" s="32"/>
       <c r="G18" s="31"/>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C19" s="29"/>
       <c r="D19" s="32"/>
       <c r="G19" s="31"/>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C20" s="29"/>
       <c r="D20" s="32"/>
       <c r="E20" s="30"/>
       <c r="G20" s="31"/>
     </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C21" s="29"/>
       <c r="D21" s="32"/>
       <c r="E21" s="30"/>
       <c r="G21" s="31"/>
     </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C22" s="29"/>
       <c r="D22" s="32"/>
       <c r="E22" s="30"/>
       <c r="G22" s="31"/>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C23" s="29"/>
       <c r="D23" s="32"/>
       <c r="E23" s="30"/>
       <c r="G23" s="31"/>
     </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C24" s="29"/>
       <c r="D24" s="33"/>
       <c r="E24" s="30"/>
       <c r="G24" s="31"/>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C25" s="29"/>
       <c r="D25" s="33"/>
       <c r="E25" s="30"/>
       <c r="G25" s="31"/>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C26" s="29"/>
       <c r="D26" s="33"/>
       <c r="E26" s="30"/>
       <c r="G26" s="31"/>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D27" s="33"/>
       <c r="E27" s="30"/>
       <c r="G27" s="31"/>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D28" s="33"/>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D29" s="33"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C13">
+  <sortState ref="A2:C13">
     <sortCondition ref="B2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5239,15 +5228,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -5270,7 +5259,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43740</v>
       </c>
@@ -5289,7 +5278,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43745</v>
       </c>
@@ -5308,7 +5297,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43746</v>
       </c>
@@ -5327,7 +5316,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -5341,7 +5330,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43750</v>
       </c>
@@ -5355,7 +5344,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43744</v>
       </c>
@@ -5375,7 +5364,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43747</v>
       </c>
@@ -5393,7 +5382,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43748</v>
       </c>
@@ -5411,7 +5400,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43743</v>
       </c>
@@ -5429,7 +5418,7 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43749</v>
       </c>
@@ -5443,7 +5432,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43739</v>
       </c>
@@ -5457,7 +5446,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43741</v>
       </c>
@@ -5477,30 +5466,30 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F14" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F15" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
       <c r="G17" s="25"/>
     </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F18" s="25"/>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
       <c r="E39" s="26"/>
       <c r="F39" s="26"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D13">
+  <sortState ref="A2:D13">
     <sortCondition ref="B2:B13"/>
     <sortCondition ref="C2:C13"/>
     <sortCondition descending="1" ref="D2:D13"/>
@@ -5514,18 +5503,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -5546,7 +5535,7 @@
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43746</v>
       </c>
@@ -5565,7 +5554,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43745</v>
       </c>
@@ -5584,7 +5573,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43740</v>
       </c>
@@ -5603,7 +5592,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -5617,7 +5606,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43748</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43747</v>
       </c>
@@ -5651,7 +5640,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43750</v>
       </c>
@@ -5668,7 +5657,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43744</v>
       </c>
@@ -5685,7 +5674,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43749</v>
       </c>
@@ -5699,7 +5688,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43743</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43741</v>
       </c>
@@ -5727,7 +5716,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43739</v>
       </c>
@@ -5741,41 +5730,41 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
       <c r="F19" s="37">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
       <c r="F20">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
         <v>140</v>
       </c>
       <c r="F24" s="38">
         <f t="shared" ref="D24:G35" ca="1" si="0">RANDBETWEEN(5000,50000)</f>
-        <v>43467</v>
+        <v>15093</v>
       </c>
       <c r="G24" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>27518</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>22169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>139</v>
       </c>
@@ -5790,14 +5779,14 @@
       </c>
       <c r="F25" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>25686</v>
+        <v>14811</v>
       </c>
       <c r="G25" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>10374</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="33" t="s">
         <v>138</v>
       </c>
@@ -5807,14 +5796,14 @@
       </c>
       <c r="F26" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>14414</v>
+        <v>19734</v>
       </c>
       <c r="G26" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>48641</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12095</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>141</v>
       </c>
@@ -5824,14 +5813,14 @@
       </c>
       <c r="F27" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>16041</v>
+        <v>44869</v>
       </c>
       <c r="G27" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>15294</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30059</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="33"/>
       <c r="C28" s="35"/>
       <c r="E28" t="s">
@@ -5839,122 +5828,122 @@
       </c>
       <c r="F28" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>21852</v>
+        <v>7598</v>
       </c>
       <c r="G28" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>25643</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6790</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="33"/>
       <c r="C29" s="35"/>
       <c r="F29" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>25174</v>
+        <v>10065</v>
       </c>
       <c r="G29" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>36658</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8684</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="C30" s="38">
         <f ca="1">RANDBETWEEN(5000,50000)</f>
-        <v>12101</v>
+        <v>33407</v>
       </c>
       <c r="D30" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>39466</v>
+        <v>16353</v>
       </c>
       <c r="E30" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>45307</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="21" x14ac:dyDescent="0.4">
+        <v>11281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="21" x14ac:dyDescent="0.35">
       <c r="A31" s="33"/>
       <c r="C31" s="38">
         <f t="shared" ref="C31:C35" ca="1" si="1">RANDBETWEEN(5000,50000)</f>
-        <v>6324</v>
+        <v>37868</v>
       </c>
       <c r="D31" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>36916</v>
+        <v>38868</v>
       </c>
       <c r="E31" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>44827</v>
+        <v>14511</v>
       </c>
       <c r="G31" s="39" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
       <c r="C32" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>28050</v>
+        <v>12253</v>
       </c>
       <c r="D32" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>25021</v>
+        <v>19642</v>
       </c>
       <c r="E32" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>40153</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5335</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="33"/>
       <c r="C33" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>7211</v>
+        <v>11898</v>
       </c>
       <c r="D33" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>25501</v>
+        <v>48982</v>
       </c>
       <c r="E33" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>16546</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9847</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="34"/>
       <c r="C34" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>12275</v>
+        <v>15201</v>
       </c>
       <c r="D34" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>22086</v>
+        <v>48204</v>
       </c>
       <c r="E34" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>34631</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>26260</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="34"/>
       <c r="C35" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>36688</v>
+        <v>26953</v>
       </c>
       <c r="D35" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>18081</v>
+        <v>20955</v>
       </c>
       <c r="E35" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>28208</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25756</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="34"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="34"/>
       <c r="D37" t="s">
         <v>147</v>
@@ -5963,7 +5952,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="34"/>
       <c r="D38" t="s">
         <v>149</v>
@@ -5972,14 +5961,14 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="34"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="34"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D11">
+  <sortState ref="A2:D11">
     <sortCondition ref="B2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5990,15 +5979,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -6021,7 +6010,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43739</v>
       </c>
@@ -6040,7 +6029,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43740</v>
       </c>
@@ -6059,7 +6048,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43741</v>
       </c>
@@ -6078,7 +6067,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -6092,7 +6081,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43743</v>
       </c>
@@ -6106,7 +6095,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43744</v>
       </c>
@@ -6120,7 +6109,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43745</v>
       </c>
@@ -6134,7 +6123,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43746</v>
       </c>
@@ -6148,7 +6137,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43747</v>
       </c>
@@ -6162,7 +6151,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43748</v>
       </c>
@@ -6176,7 +6165,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43749</v>
       </c>
@@ -6190,7 +6179,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43750</v>
       </c>
@@ -6213,15 +6202,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -6244,7 +6233,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>43739</v>
       </c>
@@ -6264,7 +6253,7 @@
       <c r="H2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43740</v>
       </c>
@@ -6284,7 +6273,7 @@
       <c r="H3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43741</v>
       </c>
@@ -6304,7 +6293,7 @@
       <c r="H4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43742</v>
       </c>
@@ -6318,7 +6307,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43743</v>
       </c>
@@ -6332,7 +6321,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43744</v>
       </c>
@@ -6346,7 +6335,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43745</v>
       </c>
@@ -6366,7 +6355,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43746</v>
       </c>
@@ -6384,7 +6373,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43747</v>
       </c>
@@ -6402,7 +6391,7 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43748</v>
       </c>
@@ -6420,7 +6409,7 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43749</v>
       </c>
@@ -6434,7 +6423,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43750</v>
       </c>
@@ -6448,7 +6437,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" s="3" t="s">
         <v>33</v>
       </c>
@@ -6456,12 +6445,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F15" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F16" s="1" t="s">
         <v>38</v>
       </c>

--- a/Excel Formulas .xlsx
+++ b/Excel Formulas .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7535FDD5-492F-48A1-BEFA-95DC517B3651}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F5FB19-61BE-4111-91E0-3E33A674F916}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12720" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3559,14 +3559,14 @@
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
       <c r="C3" s="41">
         <f ca="1">A3+B3</f>
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="D3" t="s">
         <v>221</v>
@@ -3575,20 +3575,20 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4" s="41">
         <f ca="1">A4-B4</f>
-        <v>46240</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="50">
         <f ca="1">NOW()</f>
-        <v>46245.642577662038</v>
+        <v>46252.847921875</v>
       </c>
       <c r="C6" t="s">
         <v>222</v>
@@ -3615,7 +3615,7 @@
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <f ca="1">DAY(A6)</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>225</v>
@@ -3624,7 +3624,7 @@
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <f ca="1">DATE(A8,A9,A10)</f>
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="C12" t="s">
         <v>226</v>
@@ -3659,7 +3659,7 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f ca="1">TEXT(A12,"dd")</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B16" t="str">
         <f ca="1">TEXT(A6,"mm")</f>
@@ -5757,11 +5757,11 @@
       </c>
       <c r="F24" s="38">
         <f t="shared" ref="D24:G35" ca="1" si="0">RANDBETWEEN(5000,50000)</f>
-        <v>15093</v>
+        <v>13072</v>
       </c>
       <c r="G24" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>22169</v>
+        <v>20139</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -5779,11 +5779,11 @@
       </c>
       <c r="F25" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>14811</v>
+        <v>42833</v>
       </c>
       <c r="G25" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>18109</v>
+        <v>26623</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5796,11 +5796,11 @@
       </c>
       <c r="F26" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>19734</v>
+        <v>47537</v>
       </c>
       <c r="G26" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>12095</v>
+        <v>11022</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5813,11 +5813,11 @@
       </c>
       <c r="F27" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>44869</v>
+        <v>35730</v>
       </c>
       <c r="G27" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>30059</v>
+        <v>33489</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="F28" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>7598</v>
+        <v>36939</v>
       </c>
       <c r="G28" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>6790</v>
+        <v>27128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5840,41 +5840,41 @@
       <c r="C29" s="35"/>
       <c r="F29" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>10065</v>
+        <v>37837</v>
       </c>
       <c r="G29" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>8684</v>
+        <v>45525</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="C30" s="38">
         <f ca="1">RANDBETWEEN(5000,50000)</f>
-        <v>33407</v>
+        <v>44443</v>
       </c>
       <c r="D30" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>16353</v>
+        <v>35197</v>
       </c>
       <c r="E30" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>11281</v>
+        <v>7927</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="21" x14ac:dyDescent="0.35">
       <c r="A31" s="33"/>
       <c r="C31" s="38">
         <f t="shared" ref="C31:C35" ca="1" si="1">RANDBETWEEN(5000,50000)</f>
-        <v>37868</v>
+        <v>40796</v>
       </c>
       <c r="D31" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>38868</v>
+        <v>28881</v>
       </c>
       <c r="E31" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>14511</v>
+        <v>16302</v>
       </c>
       <c r="G31" s="39" t="s">
         <v>151</v>
@@ -5884,60 +5884,60 @@
       <c r="A32" s="33"/>
       <c r="C32" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>12253</v>
+        <v>8089</v>
       </c>
       <c r="D32" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>19642</v>
+        <v>6895</v>
       </c>
       <c r="E32" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>5335</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="33"/>
       <c r="C33" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>11898</v>
+        <v>14143</v>
       </c>
       <c r="D33" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>48982</v>
+        <v>26770</v>
       </c>
       <c r="E33" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>9847</v>
+        <v>38279</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="34"/>
       <c r="C34" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>15201</v>
+        <v>43445</v>
       </c>
       <c r="D34" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>48204</v>
+        <v>11845</v>
       </c>
       <c r="E34" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>26260</v>
+        <v>12726</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="34"/>
       <c r="C35" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>26953</v>
+        <v>41977</v>
       </c>
       <c r="D35" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>20955</v>
+        <v>33719</v>
       </c>
       <c r="E35" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>25756</v>
+        <v>8915</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
